--- a/galactic_experience/one-variable/series_log.xlsx
+++ b/galactic_experience/one-variable/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -539,6 +539,61 @@
       <c r="M2" t="inlineStr">
         <is>
           <t>/home/runner/work/youtube-automation/youtube-automation/output/series/one-variable/episodes/ep94/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-09-17 19:56</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/434c6cf7652333094a8758ecb78c345c_0_1789674930.mp4</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/one-variable/episodes/ep95/shots/shot_01.mp4</t>
         </is>
       </c>
     </row>

--- a/galactic_experience/one-variable/series_log.xlsx
+++ b/galactic_experience/one-variable/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -594,6 +594,61 @@
       <c r="M3" t="inlineStr">
         <is>
           <t>/home/runner/work/youtube-automation/youtube-automation/output/series/one-variable/episodes/ep95/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09-19 18:42</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/b061cd707786975aa5dc0d19d41f0ff4_0_1789843351.mp4</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/one-variable/episodes/ep96/shots/shot_01.mp4</t>
         </is>
       </c>
     </row>

--- a/galactic_experience/one-variable/series_log.xlsx
+++ b/galactic_experience/one-variable/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -649,6 +649,61 @@
       <c r="M4" t="inlineStr">
         <is>
           <t>/home/runner/work/youtube-automation/youtube-automation/output/series/one-variable/episodes/ep96/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-09-21 20:32</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/7453786211bb4d00b0f391c422a9f7be_0_1790022701.mp4</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/one-variable/episodes/ep97/shots/shot_01.mp4</t>
         </is>
       </c>
     </row>

--- a/galactic_experience/one-variable/series_log.xlsx
+++ b/galactic_experience/one-variable/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -704,6 +704,61 @@
       <c r="M5" t="inlineStr">
         <is>
           <t>/home/runner/work/youtube-automation/youtube-automation/output/series/one-variable/episodes/ep97/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:48</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/792ed54e3fdf501b509499809861f343_0_1790192910.mp4</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/one-variable/episodes/ep98/shots/shot_01.mp4</t>
         </is>
       </c>
     </row>

--- a/galactic_experience/one-variable/series_log.xlsx
+++ b/galactic_experience/one-variable/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -759,6 +759,61 @@
       <c r="M6" t="inlineStr">
         <is>
           <t>/home/runner/work/youtube-automation/youtube-automation/output/series/one-variable/episodes/ep98/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09-25 17:17</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>210.0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/ff03bdc36b0457ed56ba4a63d596e797_0_1790356497.mp4</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/one-variable/episodes/ep99/shots/shot_01.mp4</t>
         </is>
       </c>
     </row>

--- a/galactic_experience/one-variable/series_log.xlsx
+++ b/galactic_experience/one-variable/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -814,6 +814,61 @@
       <c r="M7" t="inlineStr">
         <is>
           <t>/home/runner/work/youtube-automation/youtube-automation/output/series/one-variable/episodes/ep99/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09-29 00:16</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/4d9f5a6cde73653b179b63f32a5767db_0_1790640846.mp4</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/one-variable/episodes/ep100/shots/shot_01.mp4</t>
         </is>
       </c>
     </row>

--- a/galactic_experience/one-variable/series_log.xlsx
+++ b/galactic_experience/one-variable/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -869,6 +869,61 @@
       <c r="M8" t="inlineStr">
         <is>
           <t>/home/runner/work/youtube-automation/youtube-automation/output/series/one-variable/episodes/ep100/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-03 16:22</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/38945146728bf3eb5d2e6583e495767d_0_1791044471.mp4</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/one-variable/episodes/ep101/shots/shot_01.mp4</t>
         </is>
       </c>
     </row>

--- a/galactic_experience/one-variable/series_log.xlsx
+++ b/galactic_experience/one-variable/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -924,6 +924,61 @@
       <c r="M9" t="inlineStr">
         <is>
           <t>/home/runner/work/youtube-automation/youtube-automation/output/series/one-variable/episodes/ep101/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-07 19:13</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/4c4ff61a88eb5af7644c6144506a0c5b_0_1791400378.mp4</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/one-variable/episodes/ep102/shots/shot_01.mp4</t>
         </is>
       </c>
     </row>

--- a/galactic_experience/one-variable/series_log.xlsx
+++ b/galactic_experience/one-variable/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -982,6 +982,116 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-09 18:36</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>210.0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/6ed44bba78de64368894151fdc913dd1_0_1791570834.mp4</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/one-variable/episodes/ep103/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-11 17:52</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>210.0</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/4aa3c068f58f894908c8544d06e053fa_0_1791740654.mp4</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/one-variable/episodes/ep103/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/galactic_experience/one-variable/series_log.xlsx
+++ b/galactic_experience/one-variable/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1092,6 +1092,61 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-15 18:05</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/6953aac1165aaf4333ba57d21aaa20be_0_1792086819.mp4</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/one-variable/episodes/ep104/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/galactic_experience/one-variable/series_log.xlsx
+++ b/galactic_experience/one-variable/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1147,6 +1147,116 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-10-17 15:42</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>210.0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/1289263fa0ab29efc7cddf9c315fd676_0_1792251557.mp4</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/one-variable/episodes/ep105/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-19 19:00</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>210.0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/99b3f3c473bd2344524e5f16b8597df2_0_1792435711.mp4</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/one-variable/episodes/ep105/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/galactic_experience/one-variable/series_log.xlsx
+++ b/galactic_experience/one-variable/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1257,6 +1257,61 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-10-23 17:19</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/656c0338799805e13a3fbc337c5707ee_0_1792775574.mp4</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/one-variable/episodes/ep106/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/galactic_experience/one-variable/series_log.xlsx
+++ b/galactic_experience/one-variable/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1312,6 +1312,61 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-10-29 18:39</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/ee7588b6c580eb90b8eaa987fb850f5b_0_1793298731.mp4</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/one-variable/episodes/ep107/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
